--- a/calculations.xlsx
+++ b/calculations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0dc02c4a829257e4/Documents/Personal/projects/bluetooth-audio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="826" documentId="8_{4FB5AB32-D425-4BE6-BD36-2E3FAA4B4BF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6C4D5E3-1B8E-43B9-8994-F3424C718E1A}"/>
+  <xr:revisionPtr revIDLastSave="1025" documentId="8_{4FB5AB32-D425-4BE6-BD36-2E3FAA4B4BF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E0E0EFB-E105-4D53-B5EA-275BEC578169}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{49D08A49-7D4D-4255-9C0B-B147CF678ED3}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{49D08A49-7D4D-4255-9C0B-B147CF678ED3}"/>
   </bookViews>
   <sheets>
     <sheet name="System design" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="291">
   <si>
     <t>Ilp-p</t>
   </si>
@@ -910,6 +910,13 @@
   </si>
   <si>
     <t>Check USB footprint</t>
+  </si>
+  <si>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>Bluetooth adaptor that plugs into a 3.5mm audio jack. When in RX mode, the device recieves wireless audio from a phone and outputs it on the 3.5 mm jack.
+When in TX mode, the device receives analog audio from the 3.5 mm jack, and outputs it over bluetooth wireless to a speaker / headphones etc</t>
   </si>
 </sst>
 </file>
@@ -1060,7 +1067,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1117,6 +1124,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1287,14 +1300,14 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>449000</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>133621</xdr:rowOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>133620</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1331,13 +1344,13 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>376512</xdr:colOff>
-      <xdr:row>61</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>128534</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1375,14 +1388,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>149679</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>140141</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>295907</xdr:colOff>
-      <xdr:row>99</xdr:row>
-      <xdr:rowOff>75677</xdr:rowOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>75676</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1419,14 +1432,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>619124</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>96</xdr:row>
       <xdr:rowOff>175188</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>156952</xdr:colOff>
-      <xdr:row>110</xdr:row>
-      <xdr:rowOff>165475</xdr:rowOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>165476</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1463,13 +1476,13 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>391023</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>307817</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1507,14 +1520,14 @@
     <xdr:from>
       <xdr:col>30</xdr:col>
       <xdr:colOff>228601</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>2</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>44</xdr:col>
       <xdr:colOff>133349</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>188860</xdr:rowOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>179335</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2571,7 +2584,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FFFBAFF-8947-4084-92DD-D93B3A44A18A}">
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.06640625" style="12"/>
@@ -2933,636 +2946,703 @@
       <c r="F26" s="24"/>
       <c r="G26" s="25"/>
     </row>
-    <row r="28" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A28" s="16" t="s">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A27" s="26"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A28" s="26" t="s">
+        <v>289</v>
+      </c>
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A29" s="27" t="s">
+        <v>290</v>
+      </c>
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A30" s="26"/>
+      <c r="B30" s="26"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A31" s="26"/>
+      <c r="B31" s="26"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A32" s="26"/>
+      <c r="B32" s="26"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A33" s="26"/>
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+    </row>
+    <row r="35" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A35" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B35" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C35" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D35" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="E28" s="20" t="s">
+      <c r="E35" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="F28" s="18" t="s">
+      <c r="F35" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="G28" s="17" t="s">
+      <c r="G35" s="17" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="B30" s="15" t="s">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B37" s="15" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B31" s="9" t="s">
+    <row r="38" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="B38" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C38" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="D38" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="E31" s="21" t="b">
+      <c r="E38" s="21" t="b">
         <v>1</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F38" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="C32" s="9" t="s">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="C39" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="E32" s="21" t="b">
+      <c r="E39" s="21" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="B33" s="9" t="s">
+    <row r="40" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="B40" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C40" s="9" t="s">
         <v>168</v>
-      </c>
-      <c r="E33" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B35" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="E35" s="21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B36" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="E36" s="21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B37" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="E37" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="F37" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B39" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="G39" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="H39" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="40" spans="2:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B40" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>178</v>
       </c>
       <c r="E40" s="21" t="b">
         <v>1</v>
       </c>
-      <c r="G40" s="19" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="41" spans="2:8" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="C41" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="E41" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="G41" s="19" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="G40" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B42" s="9" t="s">
+        <v>170</v>
+      </c>
       <c r="C42" s="9" t="s">
-        <v>257</v>
+        <v>171</v>
       </c>
       <c r="E42" s="21" t="b">
         <v>1</v>
       </c>
-      <c r="G42" s="19" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8" ht="28.5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B43" s="9" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="E43" s="21" t="b">
         <v>1</v>
       </c>
-      <c r="G43" s="9" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8" ht="28.5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B44" s="9" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="E44" s="21" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="2:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C45" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="E45" s="21" t="b">
+      <c r="F44" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B46" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="G46" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="H46" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="B47" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="E47" s="21" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="E46" s="21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B47" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="E47" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="G47" s="9" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="G47" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
       <c r="C48" s="9" t="s">
-        <v>203</v>
+        <v>250</v>
       </c>
       <c r="E48" s="21" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="2:7" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="G48" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.45">
       <c r="C49" s="9" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="E49" s="21" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B50" s="10" t="s">
-        <v>214</v>
+      <c r="G49" s="19" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="B50" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="E50" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="51" spans="2:7" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B51" s="9" t="s">
-        <v>220</v>
+        <v>179</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>226</v>
+        <v>180</v>
       </c>
       <c r="E51" s="21" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="2:7" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="B52" s="9" t="s">
-        <v>215</v>
-      </c>
+    <row r="52" spans="2:7" ht="28.5" x14ac:dyDescent="0.45">
       <c r="C52" s="9" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="E52" s="21" t="b">
         <v>1</v>
       </c>
-      <c r="G52" s="9" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="53" spans="2:7" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="B53" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="C53" s="9" t="s">
-        <v>227</v>
-      </c>
+    </row>
+    <row r="53" spans="2:7" x14ac:dyDescent="0.45">
       <c r="E53" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="G53" s="9" t="s">
-        <v>219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B54" s="9" t="s">
-        <v>222</v>
+        <v>181</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>224</v>
+        <v>182</v>
       </c>
       <c r="E54" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="C55" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="E55" s="21" t="b">
         <v>1</v>
       </c>
-      <c r="G54" s="9" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B55" s="10"/>
-    </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B56" s="9" t="s">
-        <v>186</v>
-      </c>
+    </row>
+    <row r="56" spans="2:7" ht="28.5" x14ac:dyDescent="0.45">
       <c r="C56" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>188</v>
+        <v>249</v>
       </c>
       <c r="E56" s="21" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="D57" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="E57" s="21" t="b">
-        <v>1</v>
+      <c r="B57" s="10" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="58" spans="2:7" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B58" s="9" t="s">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>191</v>
+        <v>226</v>
       </c>
       <c r="E58" s="21" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:7" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="B59" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="E59" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" ht="42.75" x14ac:dyDescent="0.45">
       <c r="B60" s="9" t="s">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="D60" s="9" t="s">
-        <v>266</v>
+        <v>227</v>
       </c>
       <c r="E60" s="21" t="b">
         <v>1</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>194</v>
+        <v>219</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B61" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="E61" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B62" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="E62" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="G62" s="19" t="s">
-        <v>281</v>
-      </c>
+      <c r="B62" s="10"/>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B63" s="9" t="s">
+        <v>186</v>
+      </c>
       <c r="C63" s="9" t="s">
-        <v>196</v>
+        <v>187</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>188</v>
       </c>
       <c r="E63" s="21" t="b">
         <v>1</v>
       </c>
-      <c r="G63" s="9" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="64" spans="2:7" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C64" s="9" t="s">
-        <v>198</v>
+    </row>
+    <row r="64" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="D64" s="9" t="s">
+        <v>265</v>
       </c>
       <c r="E64" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="G64" s="9" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="65" spans="2:8" ht="28.5" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="B65" s="9" t="s">
+        <v>189</v>
+      </c>
       <c r="C65" s="9" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="E65" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="G65" s="19" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="67" spans="2:8" ht="28.5" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B67" s="9" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E67" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="68" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="C68" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="D68" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="E68" s="21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.45">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="69" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B69" s="9" t="s">
+        <v>125</v>
+      </c>
       <c r="C69" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="D69" s="9" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="E69" s="21" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="2:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B71" s="9" t="s">
+      <c r="G69" s="19" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="70" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="C70" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="E70" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G70" s="9" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="71" spans="2:7" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="C71" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="E71" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G71" s="9" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="72" spans="2:7" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="C72" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="E72" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G72" s="19" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="74" spans="2:7" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="B74" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="E74" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G74" s="9" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="75" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="C75" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="E75" s="21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="C76" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="E76" s="21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="2:7" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="B78" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="C71" s="9" t="s">
+      <c r="C78" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="E71" s="21" t="b">
+      <c r="E78" s="21" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="C72" s="9" t="s">
+    <row r="79" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="C79" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="E72" s="21" t="b">
+      <c r="E79" s="21" t="b">
         <v>1</v>
       </c>
-      <c r="F72" t="s">
+      <c r="F79" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="75" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B75" s="10" t="s">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B82" s="10" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="77" spans="2:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B77" s="9" t="s">
+    <row r="84" spans="2:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="B84" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="C77" s="9" t="s">
+      <c r="C84" s="9" t="s">
         <v>230</v>
-      </c>
-      <c r="E77" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="G77" s="19" t="s">
-        <v>258</v>
-      </c>
-      <c r="H77" s="11" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="78" spans="2:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C78" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="E78" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="G78" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="H78" s="11" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="79" spans="2:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C79" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="E79" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="G79" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="H79" s="11" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="80" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="C80" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="E80" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="H80" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="C81" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="E81" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="F81" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="82" spans="2:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C82" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="E82" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="G82" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="H82" s="11" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="83" spans="2:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C83" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="E83" s="21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="D84" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="E84" s="21" t="b">
         <v>1</v>
       </c>
+      <c r="G84" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="H84" s="11" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="85" spans="2:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="C85" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="E85" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G85" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="H85" s="11" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="86" spans="2:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B86" s="9" t="s">
-        <v>243</v>
-      </c>
       <c r="C86" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="D86" s="9" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="E86" s="21" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G86" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="H86" s="11" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="87" spans="2:8" x14ac:dyDescent="0.45">
       <c r="C87" s="9" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="E87" s="21" t="b">
         <v>0</v>
       </c>
-      <c r="G87" s="9" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B89" s="9" t="s">
-        <v>271</v>
-      </c>
+      <c r="H87" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="C88" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="E88" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F88" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="89" spans="2:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="C89" s="9" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="E89" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G89" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="H89" s="11" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="C90" s="9" t="s">
-        <v>273</v>
+        <v>239</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="E90" s="21" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="C91" s="9" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="C92" s="9" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="D91" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="E91" s="21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="2:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="B93" s="9" t="s">
+        <v>243</v>
+      </c>
       <c r="C93" s="9" t="s">
-        <v>276</v>
+        <v>244</v>
+      </c>
+      <c r="D93" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="E93" s="21" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.45">
       <c r="C94" s="9" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="C95" s="9" t="s">
-        <v>278</v>
+        <v>246</v>
+      </c>
+      <c r="E94" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G94" s="9" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="96" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B96" s="9" t="s">
+        <v>271</v>
+      </c>
       <c r="C96" s="9" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
     </row>
     <row r="97" spans="3:3" x14ac:dyDescent="0.45">
       <c r="C97" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="98" spans="3:3" x14ac:dyDescent="0.45">
+      <c r="C98" s="9" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="99" spans="3:3" x14ac:dyDescent="0.45">
+      <c r="C99" s="9" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="100" spans="3:3" x14ac:dyDescent="0.45">
+      <c r="C100" s="9" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="101" spans="3:3" x14ac:dyDescent="0.45">
+      <c r="C101" s="9" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="102" spans="3:3" x14ac:dyDescent="0.45">
+      <c r="C102" s="9" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="103" spans="3:3" x14ac:dyDescent="0.45">
+      <c r="C103" s="9" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="104" spans="3:3" x14ac:dyDescent="0.45">
+      <c r="C104" s="9" t="s">
         <v>280</v>
       </c>
     </row>
@@ -3572,21 +3652,22 @@
     <mergeCell ref="A26:G26"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G82" r:id="rId1" xr:uid="{AE6E8CD3-CE05-4E11-AB94-C2D2E53F54C1}"/>
-    <hyperlink ref="G40" r:id="rId2" xr:uid="{161879B9-8964-49BA-93E6-52B04466730F}"/>
-    <hyperlink ref="G41" r:id="rId3" xr:uid="{8E7723A3-FA5F-4A32-9BB8-45B6C2412138}"/>
-    <hyperlink ref="G42" r:id="rId4" xr:uid="{770DE760-6D01-495D-B4E3-0C55DE4558C1}"/>
-    <hyperlink ref="G39" r:id="rId5" xr:uid="{60918D76-E4D6-4E2F-9CBB-02A8988CB9A3}"/>
-    <hyperlink ref="G77" r:id="rId6" xr:uid="{976217E8-9409-4D58-8C3E-14701B3E80B2}"/>
-    <hyperlink ref="H77" r:id="rId7" xr:uid="{B4E423BD-7BA4-40A4-90D3-09CF69B23931}"/>
-    <hyperlink ref="H78" r:id="rId8" xr:uid="{1167BE93-6E02-45D3-958C-328B03C3C466}"/>
-    <hyperlink ref="H79" r:id="rId9" xr:uid="{BFA82FD4-8B89-4815-897A-A2AF8D1F9C77}"/>
-    <hyperlink ref="H82" r:id="rId10" xr:uid="{49C08944-CB5F-4181-9EAF-B9649E7C8B97}"/>
-    <hyperlink ref="G62" r:id="rId11" xr:uid="{EC24EEF0-7E46-4486-8946-2D897EFA4839}"/>
-    <hyperlink ref="G65" r:id="rId12" xr:uid="{F1B8656A-2D74-4C3D-B45E-7D20AC3B6875}"/>
+    <hyperlink ref="G89" r:id="rId1" xr:uid="{AE6E8CD3-CE05-4E11-AB94-C2D2E53F54C1}"/>
+    <hyperlink ref="G47" r:id="rId2" xr:uid="{161879B9-8964-49BA-93E6-52B04466730F}"/>
+    <hyperlink ref="G48" r:id="rId3" xr:uid="{8E7723A3-FA5F-4A32-9BB8-45B6C2412138}"/>
+    <hyperlink ref="G49" r:id="rId4" xr:uid="{770DE760-6D01-495D-B4E3-0C55DE4558C1}"/>
+    <hyperlink ref="G46" r:id="rId5" xr:uid="{60918D76-E4D6-4E2F-9CBB-02A8988CB9A3}"/>
+    <hyperlink ref="G84" r:id="rId6" xr:uid="{976217E8-9409-4D58-8C3E-14701B3E80B2}"/>
+    <hyperlink ref="H84" r:id="rId7" xr:uid="{B4E423BD-7BA4-40A4-90D3-09CF69B23931}"/>
+    <hyperlink ref="H85" r:id="rId8" xr:uid="{1167BE93-6E02-45D3-958C-328B03C3C466}"/>
+    <hyperlink ref="H86" r:id="rId9" xr:uid="{BFA82FD4-8B89-4815-897A-A2AF8D1F9C77}"/>
+    <hyperlink ref="H89" r:id="rId10" xr:uid="{49C08944-CB5F-4181-9EAF-B9649E7C8B97}"/>
+    <hyperlink ref="G69" r:id="rId11" xr:uid="{EC24EEF0-7E46-4486-8946-2D897EFA4839}"/>
+    <hyperlink ref="G72" r:id="rId12" xr:uid="{F1B8656A-2D74-4C3D-B45E-7D20AC3B6875}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId13"/>
+  <pageSetup orientation="portrait" r:id="rId13"/>
+  <drawing r:id="rId14"/>
 </worksheet>
 </file>
 
